--- a/data/broker/broker_quote_2026-07-22.xlsx
+++ b/data/broker/broker_quote_2026-07-22.xlsx
@@ -138,7 +138,7 @@
     <t/>
   </si>
   <si>
-    <t>14:26:30</t>
+    <t>06:26:30</t>
   </si>
   <si>
     <t>A</t>
@@ -168,7 +168,7 @@
     <t>华龙证券股份有限公司</t>
   </si>
   <si>
-    <t>2025-10-13</t>
+    <t>2025-10-12</t>
   </si>
   <si>
     <t>26贵经01</t>
@@ -192,7 +192,7 @@
     <t>3.0197/4.7840</t>
   </si>
   <si>
-    <t>13:36:32</t>
+    <t>05:36:32</t>
   </si>
   <si>
     <t>贵阳信用增进投资有限责任公司</t>
@@ -213,7 +213,7 @@
     <t>中德证券有限责任公司</t>
   </si>
   <si>
-    <t>2026-04-21</t>
+    <t>2026-04-20</t>
   </si>
   <si>
     <t>26长春轨交MTN006</t>
@@ -231,7 +231,7 @@
     <t>2.9578</t>
   </si>
   <si>
-    <t>10:34:28</t>
+    <t>02:34:28</t>
   </si>
   <si>
     <t>C</t>
@@ -249,7 +249,7 @@
     <t>招商银行股份有限公司</t>
   </si>
   <si>
-    <t>2026-05-27</t>
+    <t>2026-05-26</t>
   </si>
   <si>
     <t>S</t>
@@ -273,7 +273,7 @@
     <t>2.9890</t>
   </si>
   <si>
-    <t>10:22:41</t>
+    <t>02:22:41</t>
   </si>
   <si>
     <t>D-</t>
@@ -285,7 +285,7 @@
     <t>平安银行股份有限公司</t>
   </si>
   <si>
-    <t>2025-11-03</t>
+    <t>2025-11-02</t>
   </si>
   <si>
     <t>成交日期</t>

--- a/data/broker/broker_quote_2026-07-22.xlsx
+++ b/data/broker/broker_quote_2026-07-22.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="143">
   <si>
     <t>类型</t>
   </si>
@@ -105,7 +105,64 @@
     <t>主/债</t>
   </si>
   <si>
-    <t>(支持导入最多2000个债券)</t>
+    <t/>
+  </si>
+  <si>
+    <t>26太重MTN007(科创债)</t>
+  </si>
+  <si>
+    <t>102682576.IB</t>
+  </si>
+  <si>
+    <t>4.98Y+N</t>
+  </si>
+  <si>
+    <t>3.1900</t>
+  </si>
+  <si>
+    <t>0.00</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>3.1477/3.6630</t>
+  </si>
+  <si>
+    <t>4.23</t>
+  </si>
+  <si>
+    <t>07:15:21</t>
+  </si>
+  <si>
+    <t>A-</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>**</t>
+  </si>
+  <si>
+    <t>99.6097</t>
+  </si>
+  <si>
+    <t>93.33</t>
+  </si>
+  <si>
+    <t>2.8000</t>
+  </si>
+  <si>
+    <t>4/14</t>
+  </si>
+  <si>
+    <t>中国邮政储蓄银行股份有限公司</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
   </si>
   <si>
     <t>25兰新02</t>
@@ -126,16 +183,10 @@
     <t>3.00</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>3.1274</t>
   </si>
   <si>
-    <t/>
+    <t>3.26</t>
   </si>
   <si>
     <t>06:26:30</t>
@@ -144,12 +195,6 @@
     <t>A</t>
   </si>
   <si>
-    <t>--</t>
-  </si>
-  <si>
-    <t>**</t>
-  </si>
-  <si>
     <t>103.4132</t>
   </si>
   <si>
@@ -168,6 +213,9 @@
     <t>华龙证券股份有限公司</t>
   </si>
   <si>
+    <t>3.94</t>
+  </si>
+  <si>
     <t>2025-10-12</t>
   </si>
   <si>
@@ -192,6 +240,9 @@
     <t>3.0197/4.7840</t>
   </si>
   <si>
+    <t>7.03</t>
+  </si>
+  <si>
     <t>05:36:32</t>
   </si>
   <si>
@@ -213,10 +264,67 @@
     <t>中德证券有限责任公司</t>
   </si>
   <si>
+    <t>7.78</t>
+  </si>
+  <si>
     <t>2026-04-20</t>
   </si>
   <si>
-    <t>26长春轨交MTN006</t>
+    <t>24泰丰02</t>
+  </si>
+  <si>
+    <t>254402.SH</t>
+  </si>
+  <si>
+    <t>2.79Y</t>
+  </si>
+  <si>
+    <t>3.0200</t>
+  </si>
+  <si>
+    <t>3.0000</t>
+  </si>
+  <si>
+    <t>2.00</t>
+  </si>
+  <si>
+    <t>2.9796</t>
+  </si>
+  <si>
+    <t>4.04</t>
+  </si>
+  <si>
+    <t>08:24:46</t>
+  </si>
+  <si>
+    <t>新泰市财金投资集团有限公司</t>
+  </si>
+  <si>
+    <t>107.6422</t>
+  </si>
+  <si>
+    <t>23.24</t>
+  </si>
+  <si>
+    <t>13939.45</t>
+  </si>
+  <si>
+    <t>8/14</t>
+  </si>
+  <si>
+    <t>申港证券股份有限公司</t>
+  </si>
+  <si>
+    <t>2.04</t>
+  </si>
+  <si>
+    <t>2024-05-07</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>25陕建集团SCP012(科创债)</t>
   </si>
   <si>
     <t>102681950.IB</t>
@@ -225,12 +333,12 @@
     <t>9.85Y</t>
   </si>
   <si>
-    <t>3.0200</t>
-  </si>
-  <si>
     <t>2.9578</t>
   </si>
   <si>
+    <t>6.22</t>
+  </si>
+  <si>
     <t>02:34:28</t>
   </si>
   <si>
@@ -252,40 +360,43 @@
     <t>2026-05-26</t>
   </si>
   <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>25陕建集团SCP012(科创债)</t>
-  </si>
-  <si>
-    <t>012582661.IB</t>
-  </si>
-  <si>
-    <t>9D</t>
-  </si>
-  <si>
-    <t>3.0000</t>
-  </si>
-  <si>
-    <t>0.00</t>
-  </si>
-  <si>
-    <t>2.9890</t>
-  </si>
-  <si>
-    <t>02:22:41</t>
-  </si>
-  <si>
-    <t>D-</t>
-  </si>
-  <si>
-    <t>99.9510</t>
-  </si>
-  <si>
-    <t>平安银行股份有限公司</t>
-  </si>
-  <si>
-    <t>2025-11-02</t>
+    <t>全部利率</t>
+  </si>
+  <si>
+    <t>26鲁商MTN001</t>
+  </si>
+  <si>
+    <t>102681551.IB</t>
+  </si>
+  <si>
+    <t>2.75Y</t>
+  </si>
+  <si>
+    <t>2.8500</t>
+  </si>
+  <si>
+    <t>2.7675</t>
+  </si>
+  <si>
+    <t>8.25</t>
+  </si>
+  <si>
+    <t>08:08:15</t>
+  </si>
+  <si>
+    <t>100.2870</t>
+  </si>
+  <si>
+    <t>5.00</t>
+  </si>
+  <si>
+    <t>0.2502</t>
+  </si>
+  <si>
+    <t>2/14</t>
+  </si>
+  <si>
+    <t>国泰海通证券股份有限公司</t>
   </si>
   <si>
     <t>成交日期</t>
@@ -297,27 +408,15 @@
     <t>区域</t>
   </si>
   <si>
-    <t>涨跌(bp)</t>
-  </si>
-  <si>
-    <t>票面利率(%)</t>
-  </si>
-  <si>
-    <t>债券余额(亿)</t>
-  </si>
-  <si>
-    <t>到期日</t>
-  </si>
-  <si>
-    <t>YY评分</t>
-  </si>
-  <si>
-    <t>久期</t>
-  </si>
-  <si>
     <t>2026-7-22</t>
   </si>
   <si>
+    <t>太原重型机械集团有限公司</t>
+  </si>
+  <si>
+    <t>山西</t>
+  </si>
+  <si>
     <t>兰州新区城市发展投资集团有限公司</t>
   </si>
   <si>
@@ -330,16 +429,19 @@
     <t>贵州</t>
   </si>
   <si>
+    <t>山东泰丰控股集团有限公司</t>
+  </si>
+  <si>
+    <t>山东</t>
+  </si>
+  <si>
     <t>长春市轨道交通集团有限公司</t>
   </si>
   <si>
     <t>吉林</t>
   </si>
   <si>
-    <t>陕西建工集团股份有限公司</t>
-  </si>
-  <si>
-    <t>陕西</t>
+    <t>山东省商业集团有限公司</t>
   </si>
 </sst>
 </file>
@@ -716,10 +818,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AD7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="26" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="14" width="10" customWidth="1"/>
@@ -735,7 +838,7 @@
     <col min="24" max="24" width="18" customWidth="1"/>
     <col min="25" max="25" width="19" customWidth="1"/>
     <col min="26" max="26" width="13" customWidth="1"/>
-    <col min="27" max="27" width="22" customWidth="1"/>
+    <col min="27" max="27" width="30" customWidth="1"/>
     <col min="28" max="28" width="14" customWidth="1"/>
     <col min="29" max="29" width="12" customWidth="1"/>
     <col min="30" max="30" width="10" customWidth="1"/>
@@ -862,141 +965,141 @@
         <v>34</v>
       </c>
       <c r="J2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" t="s">
         <v>35</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>36</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>37</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O2" t="s">
         <v>38</v>
       </c>
-      <c r="N2" t="s">
-        <v>38</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>39</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>40</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>41</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>42</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>43</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>44</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>45</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X2" t="s">
         <v>46</v>
       </c>
-      <c r="W2" t="s">
+      <c r="Y2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z2" t="s">
         <v>47</v>
       </c>
-      <c r="X2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y2" t="s">
+      <c r="AA2" t="s">
         <v>48</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AB2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC2" t="s">
         <v>49</v>
       </c>
-      <c r="AA2" t="s">
-        <v>50</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>51</v>
-      </c>
       <c r="AD2" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" t="s">
         <v>52</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>53</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J3" t="s">
         <v>54</v>
       </c>
-      <c r="E3" t="s">
+      <c r="K3" t="s">
         <v>55</v>
       </c>
-      <c r="F3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G3" t="s">
-        <v>55</v>
-      </c>
-      <c r="H3" t="s">
-        <v>55</v>
-      </c>
-      <c r="I3" t="s">
-        <v>55</v>
-      </c>
-      <c r="J3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K3" t="s">
-        <v>57</v>
-      </c>
       <c r="L3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" t="s">
         <v>37</v>
-      </c>
-      <c r="M3" t="s">
-        <v>38</v>
       </c>
       <c r="N3" t="s">
         <v>37</v>
       </c>
       <c r="O3" t="s">
+        <v>56</v>
+      </c>
+      <c r="P3" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q3" t="s">
         <v>58</v>
       </c>
-      <c r="P3" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>59</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>42</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
+        <v>43</v>
+      </c>
+      <c r="U3" t="s">
         <v>60</v>
       </c>
-      <c r="T3" t="s">
-        <v>44</v>
-      </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>61</v>
       </c>
-      <c r="V3" t="s">
+      <c r="W3" t="s">
         <v>62</v>
       </c>
-      <c r="W3" t="s">
-        <v>37</v>
-      </c>
       <c r="X3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Y3" t="s">
         <v>63</v>
@@ -1008,197 +1111,381 @@
         <v>65</v>
       </c>
       <c r="AB3" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="AC3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AD3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J4" t="s">
+        <v>72</v>
+      </c>
+      <c r="K4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L4" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N4" t="s">
+        <v>36</v>
+      </c>
+      <c r="O4" t="s">
+        <v>74</v>
+      </c>
+      <c r="P4" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>76</v>
+      </c>
+      <c r="R4" t="s">
+        <v>59</v>
+      </c>
+      <c r="S4" t="s">
+        <v>77</v>
+      </c>
+      <c r="T4" t="s">
         <v>43</v>
       </c>
-      <c r="K4" t="s">
-        <v>40</v>
-      </c>
-      <c r="L4" t="s">
-        <v>47</v>
-      </c>
-      <c r="M4" t="s">
-        <v>38</v>
-      </c>
-      <c r="N4" t="s">
-        <v>47</v>
-      </c>
-      <c r="O4" t="s">
-        <v>71</v>
-      </c>
-      <c r="P4" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>72</v>
-      </c>
-      <c r="R4" t="s">
-        <v>73</v>
-      </c>
-      <c r="S4" t="s">
-        <v>43</v>
-      </c>
-      <c r="T4" t="s">
-        <v>44</v>
-      </c>
       <c r="U4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="V4" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="W4" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="X4" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="Y4" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="Z4" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AA4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AB4" t="s">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="AC4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AD4" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F5" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G5" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="H5" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I5" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s">
+        <v>89</v>
+      </c>
+      <c r="K5" t="s">
+        <v>90</v>
+      </c>
+      <c r="L5" t="s">
+        <v>36</v>
+      </c>
+      <c r="M5" t="s">
+        <v>36</v>
+      </c>
+      <c r="N5" t="s">
+        <v>37</v>
+      </c>
+      <c r="O5" t="s">
+        <v>91</v>
+      </c>
+      <c r="P5" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>93</v>
+      </c>
+      <c r="R5" t="s">
+        <v>59</v>
+      </c>
+      <c r="S5" t="s">
+        <v>94</v>
+      </c>
+      <c r="T5" t="s">
         <v>43</v>
       </c>
-      <c r="K5" t="s">
+      <c r="U5" t="s">
+        <v>95</v>
+      </c>
+      <c r="V5" t="s">
+        <v>96</v>
+      </c>
+      <c r="W5" t="s">
+        <v>36</v>
+      </c>
+      <c r="X5" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>101</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F6" t="s">
+        <v>88</v>
+      </c>
+      <c r="G6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I6" t="s">
+        <v>88</v>
+      </c>
+      <c r="J6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K6" t="s">
+        <v>42</v>
+      </c>
+      <c r="L6" t="s">
+        <v>62</v>
+      </c>
+      <c r="M6" t="s">
+        <v>37</v>
+      </c>
+      <c r="N6" t="s">
+        <v>62</v>
+      </c>
+      <c r="O6" t="s">
+        <v>106</v>
+      </c>
+      <c r="P6" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>108</v>
+      </c>
+      <c r="R6" t="s">
+        <v>109</v>
+      </c>
+      <c r="S6" t="s">
+        <v>42</v>
+      </c>
+      <c r="T6" t="s">
+        <v>43</v>
+      </c>
+      <c r="U6" t="s">
+        <v>110</v>
+      </c>
+      <c r="V6" t="s">
+        <v>73</v>
+      </c>
+      <c r="W6" t="s">
+        <v>42</v>
+      </c>
+      <c r="X6" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>107</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D7" t="s">
+        <v>118</v>
+      </c>
+      <c r="E7" t="s">
+        <v>119</v>
+      </c>
+      <c r="F7" t="s">
+        <v>119</v>
+      </c>
+      <c r="G7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H7" t="s">
+        <v>119</v>
+      </c>
+      <c r="I7" t="s">
+        <v>119</v>
+      </c>
+      <c r="J7" t="s">
+        <v>42</v>
+      </c>
+      <c r="K7" t="s">
+        <v>42</v>
+      </c>
+      <c r="L7" t="s">
+        <v>36</v>
+      </c>
+      <c r="M7" t="s">
+        <v>36</v>
+      </c>
+      <c r="N7" t="s">
+        <v>37</v>
+      </c>
+      <c r="O7" t="s">
+        <v>120</v>
+      </c>
+      <c r="P7" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>122</v>
+      </c>
+      <c r="R7" t="s">
+        <v>109</v>
+      </c>
+      <c r="S7" t="s">
+        <v>42</v>
+      </c>
+      <c r="T7" t="s">
+        <v>43</v>
+      </c>
+      <c r="U7" t="s">
+        <v>123</v>
+      </c>
+      <c r="V7" t="s">
+        <v>124</v>
+      </c>
+      <c r="W7" t="s">
+        <v>42</v>
+      </c>
+      <c r="X7" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>127</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC7" t="s">
         <v>84</v>
       </c>
-      <c r="L5" t="s">
-        <v>37</v>
-      </c>
-      <c r="M5" t="s">
-        <v>37</v>
-      </c>
-      <c r="N5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O5" t="s">
-        <v>85</v>
-      </c>
-      <c r="P5" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>86</v>
-      </c>
-      <c r="R5" t="s">
-        <v>87</v>
-      </c>
-      <c r="S5" t="s">
-        <v>43</v>
-      </c>
-      <c r="T5" t="s">
-        <v>44</v>
-      </c>
-      <c r="U5" t="s">
-        <v>88</v>
-      </c>
-      <c r="V5" t="s">
-        <v>43</v>
-      </c>
-      <c r="W5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X5" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>89</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>40</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>90</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>40</v>
+      <c r="AD7" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1209,375 +1496,264 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="46" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="16" width="10" customWidth="1"/>
-    <col min="17" max="17" width="13" customWidth="1"/>
-    <col min="18" max="18" width="14" customWidth="1"/>
-    <col min="19" max="22" width="10" customWidth="1"/>
-    <col min="23" max="23" width="14" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="46" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" t="s">
-        <v>6</v>
-      </c>
       <c r="J1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" t="s">
-        <v>94</v>
-      </c>
-      <c r="N1" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" t="s">
-        <v>12</v>
-      </c>
-      <c r="P1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>95</v>
-      </c>
-      <c r="R1" t="s">
-        <v>96</v>
-      </c>
-      <c r="S1" t="s">
-        <v>97</v>
-      </c>
-      <c r="T1" t="s">
-        <v>98</v>
-      </c>
-      <c r="U1" t="s">
-        <v>99</v>
-      </c>
-      <c r="V1" t="s">
-        <v>16</v>
-      </c>
-      <c r="W1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="B2" t="s">
         <v>31</v>
       </c>
       <c r="C2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I2" t="s">
         <v>32</v>
       </c>
-      <c r="D2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I2" t="s">
-        <v>34</v>
-      </c>
       <c r="J2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="K2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M2" t="s">
-        <v>40</v>
-      </c>
-      <c r="N2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O2" t="s">
-        <v>38</v>
-      </c>
-      <c r="P2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>40</v>
-      </c>
-      <c r="R2" t="s">
-        <v>40</v>
-      </c>
-      <c r="S2" t="s">
-        <v>40</v>
-      </c>
-      <c r="T2" t="s">
-        <v>40</v>
-      </c>
-      <c r="U2" t="s">
-        <v>40</v>
-      </c>
-      <c r="V2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W2" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="B3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" t="s">
         <v>52</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>53</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H3" t="s">
+        <v>135</v>
+      </c>
+      <c r="I3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G4" t="s">
+        <v>136</v>
+      </c>
+      <c r="H4" t="s">
+        <v>137</v>
+      </c>
+      <c r="I4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F5" t="s">
+        <v>92</v>
+      </c>
+      <c r="G5" t="s">
+        <v>138</v>
+      </c>
+      <c r="H5" t="s">
+        <v>139</v>
+      </c>
+      <c r="I5" t="s">
+        <v>86</v>
+      </c>
+      <c r="J5" t="s">
+        <v>43</v>
+      </c>
+      <c r="K5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" t="s">
         <v>103</v>
       </c>
-      <c r="E3" t="s">
+      <c r="C6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F6" t="s">
+        <v>107</v>
+      </c>
+      <c r="G6" t="s">
+        <v>140</v>
+      </c>
+      <c r="H6" t="s">
+        <v>141</v>
+      </c>
+      <c r="I6" t="s">
         <v>104</v>
       </c>
-      <c r="F3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3" t="s">
-        <v>55</v>
-      </c>
-      <c r="H3" t="s">
-        <v>55</v>
-      </c>
-      <c r="I3" t="s">
-        <v>55</v>
-      </c>
-      <c r="J3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K3" t="s">
-        <v>55</v>
-      </c>
-      <c r="L3" t="s">
-        <v>56</v>
-      </c>
-      <c r="M3" t="s">
-        <v>40</v>
-      </c>
-      <c r="N3" t="s">
-        <v>37</v>
-      </c>
-      <c r="O3" t="s">
-        <v>38</v>
-      </c>
-      <c r="P3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>40</v>
-      </c>
-      <c r="R3" t="s">
-        <v>40</v>
-      </c>
-      <c r="S3" t="s">
-        <v>40</v>
-      </c>
-      <c r="T3" t="s">
-        <v>40</v>
-      </c>
-      <c r="U3" t="s">
-        <v>40</v>
-      </c>
-      <c r="V3" t="s">
-        <v>59</v>
-      </c>
-      <c r="W3" t="s">
-        <v>40</v>
+      <c r="J6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" t="s">
-        <v>105</v>
-      </c>
-      <c r="E4" t="s">
-        <v>106</v>
-      </c>
-      <c r="F4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G4" t="s">
-        <v>70</v>
-      </c>
-      <c r="H4" t="s">
-        <v>70</v>
-      </c>
-      <c r="I4" t="s">
-        <v>70</v>
-      </c>
-      <c r="J4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K4" t="s">
-        <v>70</v>
-      </c>
-      <c r="L4" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E7" t="s">
+        <v>120</v>
+      </c>
+      <c r="F7" t="s">
+        <v>121</v>
+      </c>
+      <c r="G7" t="s">
+        <v>142</v>
+      </c>
+      <c r="H7" t="s">
+        <v>139</v>
+      </c>
+      <c r="I7" t="s">
+        <v>117</v>
+      </c>
+      <c r="J7" t="s">
         <v>43</v>
       </c>
-      <c r="M4" t="s">
-        <v>40</v>
-      </c>
-      <c r="N4" t="s">
-        <v>47</v>
-      </c>
-      <c r="O4" t="s">
-        <v>38</v>
-      </c>
-      <c r="P4" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>40</v>
-      </c>
-      <c r="R4" t="s">
-        <v>40</v>
-      </c>
-      <c r="S4" t="s">
-        <v>40</v>
-      </c>
-      <c r="T4" t="s">
-        <v>40</v>
-      </c>
-      <c r="U4" t="s">
-        <v>40</v>
-      </c>
-      <c r="V4" t="s">
-        <v>72</v>
-      </c>
-      <c r="W4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E5" t="s">
-        <v>108</v>
-      </c>
-      <c r="F5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H5" t="s">
-        <v>83</v>
-      </c>
-      <c r="I5" t="s">
-        <v>83</v>
-      </c>
-      <c r="J5" t="s">
-        <v>83</v>
-      </c>
-      <c r="K5" t="s">
-        <v>83</v>
-      </c>
-      <c r="L5" t="s">
-        <v>43</v>
-      </c>
-      <c r="M5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N5" t="s">
-        <v>37</v>
-      </c>
-      <c r="O5" t="s">
-        <v>37</v>
-      </c>
-      <c r="P5" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>40</v>
-      </c>
-      <c r="R5" t="s">
-        <v>40</v>
-      </c>
-      <c r="S5" t="s">
-        <v>40</v>
-      </c>
-      <c r="T5" t="s">
-        <v>40</v>
-      </c>
-      <c r="U5" t="s">
-        <v>40</v>
-      </c>
-      <c r="V5" t="s">
-        <v>86</v>
-      </c>
-      <c r="W5" t="s">
-        <v>40</v>
+      <c r="K7" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1588,375 +1764,264 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="46" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="16" width="10" customWidth="1"/>
-    <col min="17" max="17" width="13" customWidth="1"/>
-    <col min="18" max="18" width="14" customWidth="1"/>
-    <col min="19" max="22" width="10" customWidth="1"/>
-    <col min="23" max="23" width="14" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="46" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" t="s">
-        <v>6</v>
-      </c>
       <c r="J1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" t="s">
-        <v>94</v>
-      </c>
-      <c r="N1" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" t="s">
-        <v>12</v>
-      </c>
-      <c r="P1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>95</v>
-      </c>
-      <c r="R1" t="s">
-        <v>96</v>
-      </c>
-      <c r="S1" t="s">
-        <v>97</v>
-      </c>
-      <c r="T1" t="s">
-        <v>98</v>
-      </c>
-      <c r="U1" t="s">
-        <v>99</v>
-      </c>
-      <c r="V1" t="s">
-        <v>16</v>
-      </c>
-      <c r="W1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="B2" t="s">
         <v>31</v>
       </c>
       <c r="C2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I2" t="s">
         <v>32</v>
       </c>
-      <c r="D2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I2" t="s">
-        <v>34</v>
-      </c>
       <c r="J2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="K2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M2" t="s">
-        <v>40</v>
-      </c>
-      <c r="N2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O2" t="s">
-        <v>38</v>
-      </c>
-      <c r="P2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>40</v>
-      </c>
-      <c r="R2" t="s">
-        <v>40</v>
-      </c>
-      <c r="S2" t="s">
-        <v>40</v>
-      </c>
-      <c r="T2" t="s">
-        <v>40</v>
-      </c>
-      <c r="U2" t="s">
-        <v>40</v>
-      </c>
-      <c r="V2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W2" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="B3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" t="s">
         <v>52</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>53</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H3" t="s">
+        <v>135</v>
+      </c>
+      <c r="I3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G4" t="s">
+        <v>136</v>
+      </c>
+      <c r="H4" t="s">
+        <v>137</v>
+      </c>
+      <c r="I4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F5" t="s">
+        <v>92</v>
+      </c>
+      <c r="G5" t="s">
+        <v>138</v>
+      </c>
+      <c r="H5" t="s">
+        <v>139</v>
+      </c>
+      <c r="I5" t="s">
+        <v>86</v>
+      </c>
+      <c r="J5" t="s">
+        <v>43</v>
+      </c>
+      <c r="K5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" t="s">
         <v>103</v>
       </c>
-      <c r="E3" t="s">
+      <c r="C6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F6" t="s">
+        <v>107</v>
+      </c>
+      <c r="G6" t="s">
+        <v>140</v>
+      </c>
+      <c r="H6" t="s">
+        <v>141</v>
+      </c>
+      <c r="I6" t="s">
         <v>104</v>
       </c>
-      <c r="F3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3" t="s">
-        <v>55</v>
-      </c>
-      <c r="H3" t="s">
-        <v>55</v>
-      </c>
-      <c r="I3" t="s">
-        <v>55</v>
-      </c>
-      <c r="J3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K3" t="s">
-        <v>55</v>
-      </c>
-      <c r="L3" t="s">
-        <v>56</v>
-      </c>
-      <c r="M3" t="s">
-        <v>40</v>
-      </c>
-      <c r="N3" t="s">
-        <v>37</v>
-      </c>
-      <c r="O3" t="s">
-        <v>38</v>
-      </c>
-      <c r="P3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>40</v>
-      </c>
-      <c r="R3" t="s">
-        <v>40</v>
-      </c>
-      <c r="S3" t="s">
-        <v>40</v>
-      </c>
-      <c r="T3" t="s">
-        <v>40</v>
-      </c>
-      <c r="U3" t="s">
-        <v>40</v>
-      </c>
-      <c r="V3" t="s">
-        <v>59</v>
-      </c>
-      <c r="W3" t="s">
-        <v>40</v>
+      <c r="J6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" t="s">
-        <v>105</v>
-      </c>
-      <c r="E4" t="s">
-        <v>106</v>
-      </c>
-      <c r="F4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G4" t="s">
-        <v>70</v>
-      </c>
-      <c r="H4" t="s">
-        <v>70</v>
-      </c>
-      <c r="I4" t="s">
-        <v>70</v>
-      </c>
-      <c r="J4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K4" t="s">
-        <v>70</v>
-      </c>
-      <c r="L4" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E7" t="s">
+        <v>120</v>
+      </c>
+      <c r="F7" t="s">
+        <v>121</v>
+      </c>
+      <c r="G7" t="s">
+        <v>142</v>
+      </c>
+      <c r="H7" t="s">
+        <v>139</v>
+      </c>
+      <c r="I7" t="s">
+        <v>117</v>
+      </c>
+      <c r="J7" t="s">
         <v>43</v>
       </c>
-      <c r="M4" t="s">
-        <v>40</v>
-      </c>
-      <c r="N4" t="s">
-        <v>47</v>
-      </c>
-      <c r="O4" t="s">
-        <v>38</v>
-      </c>
-      <c r="P4" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>40</v>
-      </c>
-      <c r="R4" t="s">
-        <v>40</v>
-      </c>
-      <c r="S4" t="s">
-        <v>40</v>
-      </c>
-      <c r="T4" t="s">
-        <v>40</v>
-      </c>
-      <c r="U4" t="s">
-        <v>40</v>
-      </c>
-      <c r="V4" t="s">
-        <v>72</v>
-      </c>
-      <c r="W4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E5" t="s">
-        <v>108</v>
-      </c>
-      <c r="F5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H5" t="s">
-        <v>83</v>
-      </c>
-      <c r="I5" t="s">
-        <v>83</v>
-      </c>
-      <c r="J5" t="s">
-        <v>83</v>
-      </c>
-      <c r="K5" t="s">
-        <v>83</v>
-      </c>
-      <c r="L5" t="s">
-        <v>43</v>
-      </c>
-      <c r="M5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N5" t="s">
-        <v>37</v>
-      </c>
-      <c r="O5" t="s">
-        <v>37</v>
-      </c>
-      <c r="P5" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>40</v>
-      </c>
-      <c r="R5" t="s">
-        <v>40</v>
-      </c>
-      <c r="S5" t="s">
-        <v>40</v>
-      </c>
-      <c r="T5" t="s">
-        <v>40</v>
-      </c>
-      <c r="U5" t="s">
-        <v>40</v>
-      </c>
-      <c r="V5" t="s">
-        <v>86</v>
-      </c>
-      <c r="W5" t="s">
-        <v>40</v>
+      <c r="K7" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/data/broker/broker_quote_2026-07-22.xlsx
+++ b/data/broker/broker_quote_2026-07-22.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="145">
   <si>
     <t>类型</t>
   </si>
@@ -270,18 +270,60 @@
     <t>2026-04-20</t>
   </si>
   <si>
-    <t>24泰丰02</t>
-  </si>
-  <si>
-    <t>254402.SH</t>
+    <t>26长春轨交MTN006</t>
+  </si>
+  <si>
+    <t>102681950.IB</t>
+  </si>
+  <si>
+    <t>9.85Y</t>
+  </si>
+  <si>
+    <t>3.0200</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>2.9578</t>
+  </si>
+  <si>
+    <t>6.22</t>
+  </si>
+  <si>
+    <t>09:03:51</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>100.8120</t>
+  </si>
+  <si>
+    <t>0.6005</t>
+  </si>
+  <si>
+    <t>1/14</t>
+  </si>
+  <si>
+    <t>招商银行股份有限公司</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>25陕建集团SCP012(科创债)</t>
+  </si>
+  <si>
+    <t>012582661.IB</t>
   </si>
   <si>
     <t>2.79Y</t>
   </si>
   <si>
-    <t>3.0200</t>
-  </si>
-  <si>
     <t>3.0000</t>
   </si>
   <si>
@@ -321,45 +363,6 @@
     <t>2024-05-07</t>
   </si>
   <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>25陕建集团SCP012(科创债)</t>
-  </si>
-  <si>
-    <t>102681950.IB</t>
-  </si>
-  <si>
-    <t>9.85Y</t>
-  </si>
-  <si>
-    <t>2.9578</t>
-  </si>
-  <si>
-    <t>6.22</t>
-  </si>
-  <si>
-    <t>02:34:28</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>100.8120</t>
-  </si>
-  <si>
-    <t>0.6005</t>
-  </si>
-  <si>
-    <t>1/14</t>
-  </si>
-  <si>
-    <t>招商银行股份有限公司</t>
-  </si>
-  <si>
-    <t>2026-05-26</t>
-  </si>
-  <si>
     <t>全部利率</t>
   </si>
   <si>
@@ -429,19 +432,22 @@
     <t>贵州</t>
   </si>
   <si>
-    <t>山东泰丰控股集团有限公司</t>
+    <t>长春市轨道交通集团有限公司</t>
+  </si>
+  <si>
+    <t>吉林</t>
+  </si>
+  <si>
+    <t>陕西建工集团股份有限公司</t>
+  </si>
+  <si>
+    <t>陕西</t>
+  </si>
+  <si>
+    <t>山东省商业集团有限公司</t>
   </si>
   <si>
     <t>山东</t>
-  </si>
-  <si>
-    <t>长春市轨道交通集团有限公司</t>
-  </si>
-  <si>
-    <t>吉林</t>
-  </si>
-  <si>
-    <t>山东省商业集团有限公司</t>
   </si>
 </sst>
 </file>
@@ -1241,64 +1247,64 @@
         <v>88</v>
       </c>
       <c r="J5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L5" t="s">
         <v>89</v>
       </c>
-      <c r="K5" t="s">
+      <c r="M5" t="s">
+        <v>37</v>
+      </c>
+      <c r="N5" t="s">
+        <v>89</v>
+      </c>
+      <c r="O5" t="s">
         <v>90</v>
       </c>
-      <c r="L5" t="s">
-        <v>36</v>
-      </c>
-      <c r="M5" t="s">
-        <v>36</v>
-      </c>
-      <c r="N5" t="s">
-        <v>37</v>
-      </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>91</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>92</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>93</v>
       </c>
-      <c r="R5" t="s">
-        <v>59</v>
-      </c>
       <c r="S5" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="T5" t="s">
         <v>43</v>
       </c>
       <c r="U5" t="s">
+        <v>94</v>
+      </c>
+      <c r="V5" t="s">
+        <v>73</v>
+      </c>
+      <c r="W5" t="s">
+        <v>42</v>
+      </c>
+      <c r="X5" t="s">
         <v>95</v>
       </c>
-      <c r="V5" t="s">
+      <c r="Y5" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z5" t="s">
         <v>96</v>
       </c>
-      <c r="W5" t="s">
-        <v>36</v>
-      </c>
-      <c r="X5" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y5" t="s">
+      <c r="AA5" t="s">
         <v>97</v>
       </c>
-      <c r="Z5" t="s">
+      <c r="AB5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC5" t="s">
         <v>98</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>99</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>101</v>
       </c>
       <c r="AD5" t="s">
         <v>30</v>
@@ -1306,16 +1312,16 @@
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" t="s">
         <v>102</v>
-      </c>
-      <c r="B6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D6" t="s">
-        <v>105</v>
       </c>
       <c r="E6" t="s">
         <v>88</v>
@@ -1333,52 +1339,52 @@
         <v>88</v>
       </c>
       <c r="J6" t="s">
-        <v>42</v>
+        <v>103</v>
       </c>
       <c r="K6" t="s">
-        <v>42</v>
+        <v>104</v>
       </c>
       <c r="L6" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="M6" t="s">
+        <v>36</v>
+      </c>
+      <c r="N6" t="s">
         <v>37</v>
       </c>
-      <c r="N6" t="s">
-        <v>62</v>
-      </c>
       <c r="O6" t="s">
+        <v>105</v>
+      </c>
+      <c r="P6" t="s">
         <v>106</v>
       </c>
-      <c r="P6" t="s">
+      <c r="Q6" t="s">
         <v>107</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="R6" t="s">
+        <v>59</v>
+      </c>
+      <c r="S6" t="s">
         <v>108</v>
-      </c>
-      <c r="R6" t="s">
-        <v>109</v>
-      </c>
-      <c r="S6" t="s">
-        <v>42</v>
       </c>
       <c r="T6" t="s">
         <v>43</v>
       </c>
       <c r="U6" t="s">
+        <v>109</v>
+      </c>
+      <c r="V6" t="s">
         <v>110</v>
       </c>
-      <c r="V6" t="s">
-        <v>73</v>
-      </c>
       <c r="W6" t="s">
+        <v>36</v>
+      </c>
+      <c r="X6" t="s">
         <v>42</v>
       </c>
-      <c r="X6" t="s">
+      <c r="Y6" t="s">
         <v>111</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>42</v>
       </c>
       <c r="Z6" t="s">
         <v>112</v>
@@ -1387,10 +1393,10 @@
         <v>113</v>
       </c>
       <c r="AB6" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AC6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AD6" t="s">
         <v>30</v>
@@ -1398,31 +1404,31 @@
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J7" t="s">
         <v>42</v>
@@ -1440,16 +1446,16 @@
         <v>37</v>
       </c>
       <c r="O7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="R7" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="S7" t="s">
         <v>42</v>
@@ -1458,28 +1464,28 @@
         <v>43</v>
       </c>
       <c r="U7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="V7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="W7" t="s">
         <v>42</v>
       </c>
       <c r="X7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Y7" t="s">
         <v>42</v>
       </c>
       <c r="Z7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AA7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AB7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AC7" t="s">
         <v>84</v>
@@ -1513,7 +1519,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -1531,10 +1537,10 @@
         <v>15</v>
       </c>
       <c r="G1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I1" t="s">
         <v>2</v>
@@ -1548,7 +1554,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B2" t="s">
         <v>31</v>
@@ -1566,10 +1572,10 @@
         <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I2" t="s">
         <v>32</v>
@@ -1583,7 +1589,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B3" t="s">
         <v>50</v>
@@ -1601,10 +1607,10 @@
         <v>57</v>
       </c>
       <c r="G3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I3" t="s">
         <v>51</v>
@@ -1618,7 +1624,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
@@ -1636,10 +1642,10 @@
         <v>75</v>
       </c>
       <c r="G4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I4" t="s">
         <v>69</v>
@@ -1653,7 +1659,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B5" t="s">
         <v>85</v>
@@ -1665,16 +1671,16 @@
         <v>88</v>
       </c>
       <c r="E5" t="s">
+        <v>90</v>
+      </c>
+      <c r="F5" t="s">
         <v>91</v>
       </c>
-      <c r="F5" t="s">
-        <v>92</v>
-      </c>
       <c r="G5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I5" t="s">
         <v>86</v>
@@ -1688,31 +1694,31 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
         <v>88</v>
       </c>
       <c r="E6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F6" t="s">
         <v>106</v>
       </c>
-      <c r="F6" t="s">
-        <v>107</v>
-      </c>
       <c r="G6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J6" t="s">
         <v>43</v>
@@ -1723,31 +1729,31 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E7" t="s">
+        <v>121</v>
+      </c>
+      <c r="F7" t="s">
+        <v>122</v>
+      </c>
+      <c r="G7" t="s">
+        <v>143</v>
+      </c>
+      <c r="H7" t="s">
+        <v>144</v>
+      </c>
+      <c r="I7" t="s">
         <v>118</v>
-      </c>
-      <c r="D7" t="s">
-        <v>119</v>
-      </c>
-      <c r="E7" t="s">
-        <v>120</v>
-      </c>
-      <c r="F7" t="s">
-        <v>121</v>
-      </c>
-      <c r="G7" t="s">
-        <v>142</v>
-      </c>
-      <c r="H7" t="s">
-        <v>139</v>
-      </c>
-      <c r="I7" t="s">
-        <v>117</v>
       </c>
       <c r="J7" t="s">
         <v>43</v>
@@ -1781,7 +1787,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -1799,10 +1805,10 @@
         <v>15</v>
       </c>
       <c r="G1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I1" t="s">
         <v>2</v>
@@ -1816,7 +1822,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B2" t="s">
         <v>31</v>
@@ -1834,10 +1840,10 @@
         <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I2" t="s">
         <v>32</v>
@@ -1851,7 +1857,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B3" t="s">
         <v>50</v>
@@ -1869,10 +1875,10 @@
         <v>57</v>
       </c>
       <c r="G3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I3" t="s">
         <v>51</v>
@@ -1886,7 +1892,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
@@ -1904,10 +1910,10 @@
         <v>75</v>
       </c>
       <c r="G4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I4" t="s">
         <v>69</v>
@@ -1921,7 +1927,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B5" t="s">
         <v>85</v>
@@ -1933,16 +1939,16 @@
         <v>88</v>
       </c>
       <c r="E5" t="s">
+        <v>90</v>
+      </c>
+      <c r="F5" t="s">
         <v>91</v>
       </c>
-      <c r="F5" t="s">
-        <v>92</v>
-      </c>
       <c r="G5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I5" t="s">
         <v>86</v>
@@ -1956,31 +1962,31 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
         <v>88</v>
       </c>
       <c r="E6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F6" t="s">
         <v>106</v>
       </c>
-      <c r="F6" t="s">
-        <v>107</v>
-      </c>
       <c r="G6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J6" t="s">
         <v>43</v>
@@ -1991,31 +1997,31 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E7" t="s">
+        <v>121</v>
+      </c>
+      <c r="F7" t="s">
+        <v>122</v>
+      </c>
+      <c r="G7" t="s">
+        <v>143</v>
+      </c>
+      <c r="H7" t="s">
+        <v>144</v>
+      </c>
+      <c r="I7" t="s">
         <v>118</v>
-      </c>
-      <c r="D7" t="s">
-        <v>119</v>
-      </c>
-      <c r="E7" t="s">
-        <v>120</v>
-      </c>
-      <c r="F7" t="s">
-        <v>121</v>
-      </c>
-      <c r="G7" t="s">
-        <v>142</v>
-      </c>
-      <c r="H7" t="s">
-        <v>139</v>
-      </c>
-      <c r="I7" t="s">
-        <v>117</v>
       </c>
       <c r="J7" t="s">
         <v>43</v>

--- a/data/broker/broker_quote_2026-07-22.xlsx
+++ b/data/broker/broker_quote_2026-07-22.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="156">
   <si>
     <t>类型</t>
   </si>
@@ -108,6 +108,60 @@
     <t/>
   </si>
   <si>
+    <t>24云能投MTN018</t>
+  </si>
+  <si>
+    <t>102483483.IB</t>
+  </si>
+  <si>
+    <t>13.06Y</t>
+  </si>
+  <si>
+    <t>3.3400</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>3.3271</t>
+  </si>
+  <si>
+    <t>1.29</t>
+  </si>
+  <si>
+    <t>10:06:45</t>
+  </si>
+  <si>
+    <t>D+</t>
+  </si>
+  <si>
+    <t>**</t>
+  </si>
+  <si>
+    <t>96.1639</t>
+  </si>
+  <si>
+    <t>0.64</t>
+  </si>
+  <si>
+    <t>0.0962</t>
+  </si>
+  <si>
+    <t>1/14</t>
+  </si>
+  <si>
+    <t>中国建设银行股份有限公司</t>
+  </si>
+  <si>
+    <t>2024-08-08</t>
+  </si>
+  <si>
     <t>26太重MTN007(科创债)</t>
   </si>
   <si>
@@ -123,12 +177,6 @@
     <t>0.00</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>3.1477/3.6630</t>
   </si>
   <si>
@@ -141,12 +189,6 @@
     <t>A-</t>
   </si>
   <si>
-    <t>--</t>
-  </si>
-  <si>
-    <t>**</t>
-  </si>
-  <si>
     <t>99.6097</t>
   </si>
   <si>
@@ -270,6 +312,9 @@
     <t>2026-04-20</t>
   </si>
   <si>
+    <t>S</t>
+  </si>
+  <si>
     <t>26长春轨交MTN006</t>
   </si>
   <si>
@@ -303,16 +348,13 @@
     <t>0.6005</t>
   </si>
   <si>
-    <t>1/14</t>
-  </si>
-  <si>
     <t>招商银行股份有限公司</t>
   </si>
   <si>
     <t>2026-05-26</t>
   </si>
   <si>
-    <t>S</t>
+    <t>全部利率</t>
   </si>
   <si>
     <t>25陕建集团SCP012(科创债)</t>
@@ -321,49 +363,34 @@
     <t>012582661.IB</t>
   </si>
   <si>
-    <t>2.79Y</t>
+    <t>9D</t>
   </si>
   <si>
     <t>3.0000</t>
   </si>
   <si>
-    <t>2.00</t>
-  </si>
-  <si>
-    <t>2.9796</t>
-  </si>
-  <si>
-    <t>4.04</t>
-  </si>
-  <si>
-    <t>08:24:46</t>
-  </si>
-  <si>
-    <t>新泰市财金投资集团有限公司</t>
-  </si>
-  <si>
-    <t>107.6422</t>
-  </si>
-  <si>
-    <t>23.24</t>
-  </si>
-  <si>
-    <t>13939.45</t>
-  </si>
-  <si>
-    <t>8/14</t>
-  </si>
-  <si>
-    <t>申港证券股份有限公司</t>
-  </si>
-  <si>
-    <t>2.04</t>
-  </si>
-  <si>
-    <t>2024-05-07</t>
-  </si>
-  <si>
-    <t>全部利率</t>
+    <t>2.9890</t>
+  </si>
+  <si>
+    <t>1.10</t>
+  </si>
+  <si>
+    <t>02:22:41</t>
+  </si>
+  <si>
+    <t>D-</t>
+  </si>
+  <si>
+    <t>99.9510</t>
+  </si>
+  <si>
+    <t>平安银行股份有限公司</t>
+  </si>
+  <si>
+    <t>2025-11-02</t>
+  </si>
+  <si>
+    <t>地方债</t>
   </si>
   <si>
     <t>26鲁商MTN001</t>
@@ -412,6 +439,12 @@
   </si>
   <si>
     <t>2026-7-22</t>
+  </si>
+  <si>
+    <t>云南省能源集团有限公司</t>
+  </si>
+  <si>
+    <t>云南</t>
   </si>
   <si>
     <t>太原重型机械集团有限公司</t>
@@ -824,7 +857,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AD8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -971,7 +1004,7 @@
         <v>34</v>
       </c>
       <c r="J2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K2" t="s">
         <v>35</v>
@@ -998,37 +1031,37 @@
         <v>41</v>
       </c>
       <c r="S2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T2" t="s">
         <v>42</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>43</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>44</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
+        <v>35</v>
+      </c>
+      <c r="X2" t="s">
         <v>45</v>
       </c>
-      <c r="W2" t="s">
-        <v>36</v>
-      </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z2" t="s">
         <v>46</v>
       </c>
-      <c r="Y2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>47</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>48</v>
       </c>
       <c r="AB2" t="s">
         <v>39</v>
       </c>
       <c r="AC2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AD2" t="s">
         <v>30</v>
@@ -1039,34 +1072,34 @@
         <v>30</v>
       </c>
       <c r="B3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" t="s">
         <v>50</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>51</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>52</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I3" t="s">
+        <v>52</v>
+      </c>
+      <c r="J3" t="s">
+        <v>52</v>
+      </c>
+      <c r="K3" t="s">
         <v>53</v>
-      </c>
-      <c r="F3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G3" t="s">
-        <v>53</v>
-      </c>
-      <c r="H3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I3" t="s">
-        <v>53</v>
-      </c>
-      <c r="J3" t="s">
-        <v>54</v>
-      </c>
-      <c r="K3" t="s">
-        <v>55</v>
       </c>
       <c r="L3" t="s">
         <v>36</v>
@@ -1075,52 +1108,52 @@
         <v>37</v>
       </c>
       <c r="N3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O3" t="s">
+        <v>54</v>
+      </c>
+      <c r="P3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q3" t="s">
         <v>56</v>
       </c>
-      <c r="P3" t="s">
+      <c r="R3" t="s">
         <v>57</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="S3" t="s">
+        <v>35</v>
+      </c>
+      <c r="T3" t="s">
+        <v>42</v>
+      </c>
+      <c r="U3" t="s">
         <v>58</v>
       </c>
-      <c r="R3" t="s">
+      <c r="V3" t="s">
         <v>59</v>
       </c>
-      <c r="S3" t="s">
-        <v>42</v>
-      </c>
-      <c r="T3" t="s">
-        <v>43</v>
-      </c>
-      <c r="U3" t="s">
+      <c r="W3" t="s">
+        <v>36</v>
+      </c>
+      <c r="X3" t="s">
         <v>60</v>
       </c>
-      <c r="V3" t="s">
+      <c r="Y3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z3" t="s">
         <v>61</v>
       </c>
-      <c r="W3" t="s">
+      <c r="AA3" t="s">
         <v>62</v>
       </c>
-      <c r="X3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y3" t="s">
+      <c r="AB3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC3" t="s">
         <v>63</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>65</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>66</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>67</v>
       </c>
       <c r="AD3" t="s">
         <v>30</v>
@@ -1131,34 +1164,34 @@
         <v>30</v>
       </c>
       <c r="B4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I4" t="s">
+        <v>67</v>
+      </c>
+      <c r="J4" t="s">
         <v>68</v>
       </c>
-      <c r="C4" t="s">
+      <c r="K4" t="s">
         <v>69</v>
-      </c>
-      <c r="D4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G4" t="s">
-        <v>71</v>
-      </c>
-      <c r="H4" t="s">
-        <v>71</v>
-      </c>
-      <c r="I4" t="s">
-        <v>71</v>
-      </c>
-      <c r="J4" t="s">
-        <v>72</v>
-      </c>
-      <c r="K4" t="s">
-        <v>73</v>
       </c>
       <c r="L4" t="s">
         <v>36</v>
@@ -1167,52 +1200,52 @@
         <v>37</v>
       </c>
       <c r="N4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O4" t="s">
+        <v>70</v>
+      </c>
+      <c r="P4" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>72</v>
+      </c>
+      <c r="R4" t="s">
+        <v>73</v>
+      </c>
+      <c r="S4" t="s">
+        <v>35</v>
+      </c>
+      <c r="T4" t="s">
+        <v>42</v>
+      </c>
+      <c r="U4" t="s">
         <v>74</v>
       </c>
-      <c r="P4" t="s">
+      <c r="V4" t="s">
         <v>75</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="W4" t="s">
         <v>76</v>
       </c>
-      <c r="R4" t="s">
-        <v>59</v>
-      </c>
-      <c r="S4" t="s">
+      <c r="X4" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y4" t="s">
         <v>77</v>
       </c>
-      <c r="T4" t="s">
-        <v>43</v>
-      </c>
-      <c r="U4" t="s">
+      <c r="Z4" t="s">
         <v>78</v>
       </c>
-      <c r="V4" t="s">
+      <c r="AA4" t="s">
         <v>79</v>
       </c>
-      <c r="W4" t="s">
-        <v>36</v>
-      </c>
-      <c r="X4" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y4" t="s">
+      <c r="AB4" t="s">
         <v>80</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AC4" t="s">
         <v>81</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>82</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>83</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>84</v>
       </c>
       <c r="AD4" t="s">
         <v>30</v>
@@ -1223,85 +1256,85 @@
         <v>30</v>
       </c>
       <c r="B5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E5" t="s">
         <v>85</v>
       </c>
-      <c r="C5" t="s">
+      <c r="F5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H5" t="s">
+        <v>85</v>
+      </c>
+      <c r="I5" t="s">
+        <v>85</v>
+      </c>
+      <c r="J5" t="s">
         <v>86</v>
       </c>
-      <c r="D5" t="s">
+      <c r="K5" t="s">
         <v>87</v>
       </c>
-      <c r="E5" t="s">
-        <v>88</v>
-      </c>
-      <c r="F5" t="s">
-        <v>88</v>
-      </c>
-      <c r="G5" t="s">
-        <v>88</v>
-      </c>
-      <c r="H5" t="s">
-        <v>88</v>
-      </c>
-      <c r="I5" t="s">
-        <v>88</v>
-      </c>
-      <c r="J5" t="s">
-        <v>42</v>
-      </c>
-      <c r="K5" t="s">
-        <v>42</v>
-      </c>
       <c r="L5" t="s">
-        <v>89</v>
+        <v>36</v>
       </c>
       <c r="M5" t="s">
         <v>37</v>
       </c>
       <c r="N5" t="s">
+        <v>36</v>
+      </c>
+      <c r="O5" t="s">
+        <v>88</v>
+      </c>
+      <c r="P5" t="s">
         <v>89</v>
       </c>
-      <c r="O5" t="s">
+      <c r="Q5" t="s">
         <v>90</v>
       </c>
-      <c r="P5" t="s">
+      <c r="R5" t="s">
+        <v>73</v>
+      </c>
+      <c r="S5" t="s">
         <v>91</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="T5" t="s">
+        <v>42</v>
+      </c>
+      <c r="U5" t="s">
         <v>92</v>
       </c>
-      <c r="R5" t="s">
+      <c r="V5" t="s">
         <v>93</v>
       </c>
-      <c r="S5" t="s">
-        <v>42</v>
-      </c>
-      <c r="T5" t="s">
-        <v>43</v>
-      </c>
-      <c r="U5" t="s">
+      <c r="W5" t="s">
+        <v>36</v>
+      </c>
+      <c r="X5" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y5" t="s">
         <v>94</v>
       </c>
-      <c r="V5" t="s">
-        <v>73</v>
-      </c>
-      <c r="W5" t="s">
-        <v>42</v>
-      </c>
-      <c r="X5" t="s">
+      <c r="Z5" t="s">
         <v>95</v>
       </c>
-      <c r="Y5" t="s">
-        <v>42</v>
-      </c>
-      <c r="Z5" t="s">
+      <c r="AA5" t="s">
         <v>96</v>
       </c>
-      <c r="AA5" t="s">
+      <c r="AB5" t="s">
         <v>97</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>91</v>
       </c>
       <c r="AC5" t="s">
         <v>98</v>
@@ -1324,34 +1357,34 @@
         <v>102</v>
       </c>
       <c r="E6" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="F6" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="G6" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="H6" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="I6" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="J6" t="s">
-        <v>103</v>
+        <v>35</v>
       </c>
       <c r="K6" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6" t="s">
         <v>104</v>
       </c>
-      <c r="L6" t="s">
-        <v>36</v>
-      </c>
       <c r="M6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N6" t="s">
-        <v>37</v>
+        <v>104</v>
       </c>
       <c r="O6" t="s">
         <v>105</v>
@@ -1363,40 +1396,40 @@
         <v>107</v>
       </c>
       <c r="R6" t="s">
-        <v>59</v>
+        <v>108</v>
       </c>
       <c r="S6" t="s">
-        <v>108</v>
+        <v>35</v>
       </c>
       <c r="T6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="U6" t="s">
         <v>109</v>
       </c>
       <c r="V6" t="s">
+        <v>87</v>
+      </c>
+      <c r="W6" t="s">
+        <v>35</v>
+      </c>
+      <c r="X6" t="s">
         <v>110</v>
       </c>
-      <c r="W6" t="s">
-        <v>36</v>
-      </c>
-      <c r="X6" t="s">
-        <v>42</v>
-      </c>
       <c r="Y6" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA6" t="s">
         <v>111</v>
       </c>
-      <c r="Z6" t="s">
+      <c r="AB6" t="s">
+        <v>106</v>
+      </c>
+      <c r="AC6" t="s">
         <v>112</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>113</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>114</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>115</v>
       </c>
       <c r="AD6" t="s">
         <v>30</v>
@@ -1404,37 +1437,37 @@
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D7" t="s">
         <v>116</v>
       </c>
-      <c r="B7" t="s">
+      <c r="E7" t="s">
         <v>117</v>
       </c>
-      <c r="C7" t="s">
-        <v>118</v>
-      </c>
-      <c r="D7" t="s">
-        <v>119</v>
-      </c>
-      <c r="E7" t="s">
-        <v>120</v>
-      </c>
       <c r="F7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="J7" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="K7" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="L7" t="s">
         <v>36</v>
@@ -1446,51 +1479,143 @@
         <v>37</v>
       </c>
       <c r="O7" t="s">
+        <v>118</v>
+      </c>
+      <c r="P7" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>120</v>
+      </c>
+      <c r="R7" t="s">
         <v>121</v>
       </c>
-      <c r="P7" t="s">
+      <c r="S7" t="s">
+        <v>35</v>
+      </c>
+      <c r="T7" t="s">
+        <v>42</v>
+      </c>
+      <c r="U7" t="s">
         <v>122</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="V7" t="s">
+        <v>35</v>
+      </c>
+      <c r="W7" t="s">
+        <v>35</v>
+      </c>
+      <c r="X7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA7" t="s">
         <v>123</v>
       </c>
-      <c r="R7" t="s">
-        <v>93</v>
-      </c>
-      <c r="S7" t="s">
+      <c r="AB7" t="s">
+        <v>119</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>124</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C8" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" t="s">
+        <v>128</v>
+      </c>
+      <c r="E8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F8" t="s">
+        <v>129</v>
+      </c>
+      <c r="G8" t="s">
+        <v>129</v>
+      </c>
+      <c r="H8" t="s">
+        <v>129</v>
+      </c>
+      <c r="I8" t="s">
+        <v>129</v>
+      </c>
+      <c r="J8" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L8" t="s">
+        <v>36</v>
+      </c>
+      <c r="M8" t="s">
+        <v>36</v>
+      </c>
+      <c r="N8" t="s">
+        <v>37</v>
+      </c>
+      <c r="O8" t="s">
+        <v>130</v>
+      </c>
+      <c r="P8" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>132</v>
+      </c>
+      <c r="R8" t="s">
+        <v>108</v>
+      </c>
+      <c r="S8" t="s">
+        <v>35</v>
+      </c>
+      <c r="T8" t="s">
         <v>42</v>
       </c>
-      <c r="T7" t="s">
-        <v>43</v>
-      </c>
-      <c r="U7" t="s">
-        <v>124</v>
-      </c>
-      <c r="V7" t="s">
-        <v>125</v>
-      </c>
-      <c r="W7" t="s">
-        <v>42</v>
-      </c>
-      <c r="X7" t="s">
-        <v>126</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>42</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>127</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>128</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>122</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>84</v>
-      </c>
-      <c r="AD7" t="s">
+      <c r="U8" t="s">
+        <v>133</v>
+      </c>
+      <c r="V8" t="s">
+        <v>134</v>
+      </c>
+      <c r="W8" t="s">
+        <v>35</v>
+      </c>
+      <c r="X8" t="s">
+        <v>135</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>137</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>131</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>98</v>
+      </c>
+      <c r="AD8" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1502,7 +1627,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1519,7 +1644,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -1537,10 +1662,10 @@
         <v>15</v>
       </c>
       <c r="G1" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="H1" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I1" t="s">
         <v>2</v>
@@ -1554,7 +1679,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B2" t="s">
         <v>31</v>
@@ -1572,16 +1697,16 @@
         <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="H2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="I2" t="s">
         <v>32</v>
       </c>
       <c r="J2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K2" t="s">
         <v>30</v>
@@ -1589,34 +1714,34 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H3" t="s">
+        <v>145</v>
+      </c>
+      <c r="I3" t="s">
         <v>50</v>
       </c>
-      <c r="C3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G3" t="s">
-        <v>135</v>
-      </c>
-      <c r="H3" t="s">
-        <v>136</v>
-      </c>
-      <c r="I3" t="s">
-        <v>51</v>
-      </c>
       <c r="J3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K3" t="s">
         <v>30</v>
@@ -1624,34 +1749,34 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" t="s">
         <v>70</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>71</v>
       </c>
-      <c r="E4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F4" t="s">
-        <v>75</v>
-      </c>
       <c r="G4" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="H4" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="J4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K4" t="s">
         <v>30</v>
@@ -1659,34 +1784,34 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" t="s">
         <v>85</v>
       </c>
-      <c r="C5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>88</v>
       </c>
-      <c r="E5" t="s">
-        <v>90</v>
-      </c>
       <c r="F5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G5" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="H5" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="I5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K5" t="s">
         <v>30</v>
@@ -1694,7 +1819,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B6" t="s">
         <v>100</v>
@@ -1703,7 +1828,7 @@
         <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s">
         <v>105</v>
@@ -1712,16 +1837,16 @@
         <v>106</v>
       </c>
       <c r="G6" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="H6" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="I6" t="s">
         <v>101</v>
       </c>
       <c r="J6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K6" t="s">
         <v>30</v>
@@ -1729,36 +1854,71 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D7" t="s">
         <v>117</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
+        <v>118</v>
+      </c>
+      <c r="F7" t="s">
         <v>119</v>
       </c>
-      <c r="D7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E7" t="s">
-        <v>121</v>
-      </c>
-      <c r="F7" t="s">
-        <v>122</v>
-      </c>
       <c r="G7" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="H7" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="I7" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="J7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C8" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" t="s">
+        <v>129</v>
+      </c>
+      <c r="E8" t="s">
+        <v>130</v>
+      </c>
+      <c r="F8" t="s">
+        <v>131</v>
+      </c>
+      <c r="G8" t="s">
+        <v>154</v>
+      </c>
+      <c r="H8" t="s">
+        <v>155</v>
+      </c>
+      <c r="I8" t="s">
+        <v>127</v>
+      </c>
+      <c r="J8" t="s">
+        <v>42</v>
+      </c>
+      <c r="K8" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1770,7 +1930,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1787,7 +1947,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -1805,10 +1965,10 @@
         <v>15</v>
       </c>
       <c r="G1" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="H1" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="I1" t="s">
         <v>2</v>
@@ -1822,7 +1982,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B2" t="s">
         <v>31</v>
@@ -1840,16 +2000,16 @@
         <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="H2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="I2" t="s">
         <v>32</v>
       </c>
       <c r="J2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K2" t="s">
         <v>30</v>
@@ -1857,34 +2017,34 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H3" t="s">
+        <v>145</v>
+      </c>
+      <c r="I3" t="s">
         <v>50</v>
       </c>
-      <c r="C3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G3" t="s">
-        <v>135</v>
-      </c>
-      <c r="H3" t="s">
-        <v>136</v>
-      </c>
-      <c r="I3" t="s">
-        <v>51</v>
-      </c>
       <c r="J3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K3" t="s">
         <v>30</v>
@@ -1892,34 +2052,34 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" t="s">
         <v>70</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>71</v>
       </c>
-      <c r="E4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F4" t="s">
-        <v>75</v>
-      </c>
       <c r="G4" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="H4" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="J4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K4" t="s">
         <v>30</v>
@@ -1927,34 +2087,34 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" t="s">
         <v>85</v>
       </c>
-      <c r="C5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>88</v>
       </c>
-      <c r="E5" t="s">
-        <v>90</v>
-      </c>
       <c r="F5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G5" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="H5" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="I5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K5" t="s">
         <v>30</v>
@@ -1962,7 +2122,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B6" t="s">
         <v>100</v>
@@ -1971,7 +2131,7 @@
         <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s">
         <v>105</v>
@@ -1980,16 +2140,16 @@
         <v>106</v>
       </c>
       <c r="G6" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="H6" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="I6" t="s">
         <v>101</v>
       </c>
       <c r="J6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K6" t="s">
         <v>30</v>
@@ -1997,36 +2157,71 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D7" t="s">
         <v>117</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
+        <v>118</v>
+      </c>
+      <c r="F7" t="s">
         <v>119</v>
       </c>
-      <c r="D7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E7" t="s">
-        <v>121</v>
-      </c>
-      <c r="F7" t="s">
-        <v>122</v>
-      </c>
       <c r="G7" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="H7" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="I7" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="J7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C8" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" t="s">
+        <v>129</v>
+      </c>
+      <c r="E8" t="s">
+        <v>130</v>
+      </c>
+      <c r="F8" t="s">
+        <v>131</v>
+      </c>
+      <c r="G8" t="s">
+        <v>154</v>
+      </c>
+      <c r="H8" t="s">
+        <v>155</v>
+      </c>
+      <c r="I8" t="s">
+        <v>127</v>
+      </c>
+      <c r="J8" t="s">
+        <v>42</v>
+      </c>
+      <c r="K8" t="s">
         <v>30</v>
       </c>
     </row>

--- a/data/broker/broker_quote_2026-07-22.xlsx
+++ b/data/broker/broker_quote_2026-07-22.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="148">
   <si>
     <t>类型</t>
   </si>
@@ -132,9 +132,6 @@
     <t>3.3271</t>
   </si>
   <si>
-    <t>1.29</t>
-  </si>
-  <si>
     <t>10:06:45</t>
   </si>
   <si>
@@ -180,9 +177,6 @@
     <t>3.1477/3.6630</t>
   </si>
   <si>
-    <t>4.23</t>
-  </si>
-  <si>
     <t>07:15:21</t>
   </si>
   <si>
@@ -228,9 +222,6 @@
     <t>3.1274</t>
   </si>
   <si>
-    <t>3.26</t>
-  </si>
-  <si>
     <t>06:26:30</t>
   </si>
   <si>
@@ -255,9 +246,6 @@
     <t>华龙证券股份有限公司</t>
   </si>
   <si>
-    <t>3.94</t>
-  </si>
-  <si>
     <t>2025-10-12</t>
   </si>
   <si>
@@ -282,9 +270,6 @@
     <t>3.0197/4.7840</t>
   </si>
   <si>
-    <t>7.03</t>
-  </si>
-  <si>
     <t>05:36:32</t>
   </si>
   <si>
@@ -306,9 +291,6 @@
     <t>中德证券有限责任公司</t>
   </si>
   <si>
-    <t>7.78</t>
-  </si>
-  <si>
     <t>2026-04-20</t>
   </si>
   <si>
@@ -327,15 +309,15 @@
     <t>3.0200</t>
   </si>
   <si>
+    <t>2.00</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
     <t>2.9578</t>
   </si>
   <si>
-    <t>6.22</t>
-  </si>
-  <si>
     <t>09:03:51</t>
   </si>
   <si>
@@ -372,9 +354,6 @@
     <t>2.9890</t>
   </si>
   <si>
-    <t>1.10</t>
-  </si>
-  <si>
     <t>02:22:41</t>
   </si>
   <si>
@@ -406,9 +385,6 @@
   </si>
   <si>
     <t>2.7675</t>
-  </si>
-  <si>
-    <t>8.25</t>
   </si>
   <si>
     <t>08:08:15</t>
@@ -1007,7 +983,7 @@
         <v>35</v>
       </c>
       <c r="K2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L2" t="s">
         <v>36</v>
@@ -1022,46 +998,46 @@
         <v>38</v>
       </c>
       <c r="P2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q2" t="s">
         <v>39</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>40</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T2" t="s">
         <v>41</v>
       </c>
-      <c r="S2" t="s">
-        <v>35</v>
-      </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>42</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>43</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
+        <v>35</v>
+      </c>
+      <c r="X2" t="s">
         <v>44</v>
       </c>
-      <c r="W2" t="s">
-        <v>35</v>
-      </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z2" t="s">
         <v>45</v>
       </c>
-      <c r="Y2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>46</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AB2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC2" t="s">
         <v>47</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>48</v>
       </c>
       <c r="AD2" t="s">
         <v>30</v>
@@ -1072,34 +1048,34 @@
         <v>30</v>
       </c>
       <c r="B3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" t="s">
         <v>49</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>50</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>51</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K3" t="s">
         <v>52</v>
-      </c>
-      <c r="F3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H3" t="s">
-        <v>52</v>
-      </c>
-      <c r="I3" t="s">
-        <v>52</v>
-      </c>
-      <c r="J3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K3" t="s">
-        <v>53</v>
       </c>
       <c r="L3" t="s">
         <v>36</v>
@@ -1111,49 +1087,49 @@
         <v>36</v>
       </c>
       <c r="O3" t="s">
+        <v>53</v>
+      </c>
+      <c r="P3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q3" t="s">
         <v>54</v>
       </c>
-      <c r="P3" t="s">
+      <c r="R3" t="s">
         <v>55</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="S3" t="s">
+        <v>35</v>
+      </c>
+      <c r="T3" t="s">
+        <v>41</v>
+      </c>
+      <c r="U3" t="s">
         <v>56</v>
       </c>
-      <c r="R3" t="s">
+      <c r="V3" t="s">
         <v>57</v>
-      </c>
-      <c r="S3" t="s">
-        <v>35</v>
-      </c>
-      <c r="T3" t="s">
-        <v>42</v>
-      </c>
-      <c r="U3" t="s">
-        <v>58</v>
-      </c>
-      <c r="V3" t="s">
-        <v>59</v>
       </c>
       <c r="W3" t="s">
         <v>36</v>
       </c>
       <c r="X3" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA3" t="s">
         <v>60</v>
       </c>
-      <c r="Y3" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z3" t="s">
+      <c r="AB3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC3" t="s">
         <v>61</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>62</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>55</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>63</v>
       </c>
       <c r="AD3" t="s">
         <v>30</v>
@@ -1164,34 +1140,34 @@
         <v>30</v>
       </c>
       <c r="B4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" t="s">
         <v>64</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>65</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H4" t="s">
+        <v>65</v>
+      </c>
+      <c r="I4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J4" t="s">
         <v>66</v>
       </c>
-      <c r="E4" t="s">
+      <c r="K4" t="s">
         <v>67</v>
-      </c>
-      <c r="F4" t="s">
-        <v>67</v>
-      </c>
-      <c r="G4" t="s">
-        <v>67</v>
-      </c>
-      <c r="H4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I4" t="s">
-        <v>67</v>
-      </c>
-      <c r="J4" t="s">
-        <v>68</v>
-      </c>
-      <c r="K4" t="s">
-        <v>69</v>
       </c>
       <c r="L4" t="s">
         <v>36</v>
@@ -1203,49 +1179,49 @@
         <v>37</v>
       </c>
       <c r="O4" t="s">
+        <v>68</v>
+      </c>
+      <c r="P4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>69</v>
+      </c>
+      <c r="R4" t="s">
         <v>70</v>
       </c>
-      <c r="P4" t="s">
+      <c r="S4" t="s">
+        <v>35</v>
+      </c>
+      <c r="T4" t="s">
+        <v>41</v>
+      </c>
+      <c r="U4" t="s">
         <v>71</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="V4" t="s">
         <v>72</v>
       </c>
-      <c r="R4" t="s">
+      <c r="W4" t="s">
         <v>73</v>
       </c>
-      <c r="S4" t="s">
-        <v>35</v>
-      </c>
-      <c r="T4" t="s">
-        <v>42</v>
-      </c>
-      <c r="U4" t="s">
+      <c r="X4" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y4" t="s">
         <v>74</v>
       </c>
-      <c r="V4" t="s">
+      <c r="Z4" t="s">
         <v>75</v>
       </c>
-      <c r="W4" t="s">
+      <c r="AA4" t="s">
         <v>76</v>
       </c>
-      <c r="X4" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y4" t="s">
+      <c r="AB4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC4" t="s">
         <v>77</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>81</v>
       </c>
       <c r="AD4" t="s">
         <v>30</v>
@@ -1256,34 +1232,34 @@
         <v>30</v>
       </c>
       <c r="B5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H5" t="s">
+        <v>81</v>
+      </c>
+      <c r="I5" t="s">
+        <v>81</v>
+      </c>
+      <c r="J5" t="s">
         <v>82</v>
       </c>
-      <c r="C5" t="s">
+      <c r="K5" t="s">
         <v>83</v>
-      </c>
-      <c r="D5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E5" t="s">
-        <v>85</v>
-      </c>
-      <c r="F5" t="s">
-        <v>85</v>
-      </c>
-      <c r="G5" t="s">
-        <v>85</v>
-      </c>
-      <c r="H5" t="s">
-        <v>85</v>
-      </c>
-      <c r="I5" t="s">
-        <v>85</v>
-      </c>
-      <c r="J5" t="s">
-        <v>86</v>
-      </c>
-      <c r="K5" t="s">
-        <v>87</v>
       </c>
       <c r="L5" t="s">
         <v>36</v>
@@ -1295,28 +1271,28 @@
         <v>36</v>
       </c>
       <c r="O5" t="s">
+        <v>84</v>
+      </c>
+      <c r="P5" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>85</v>
+      </c>
+      <c r="R5" t="s">
+        <v>70</v>
+      </c>
+      <c r="S5" t="s">
+        <v>86</v>
+      </c>
+      <c r="T5" t="s">
+        <v>41</v>
+      </c>
+      <c r="U5" t="s">
+        <v>87</v>
+      </c>
+      <c r="V5" t="s">
         <v>88</v>
-      </c>
-      <c r="P5" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>90</v>
-      </c>
-      <c r="R5" t="s">
-        <v>73</v>
-      </c>
-      <c r="S5" t="s">
-        <v>91</v>
-      </c>
-      <c r="T5" t="s">
-        <v>42</v>
-      </c>
-      <c r="U5" t="s">
-        <v>92</v>
-      </c>
-      <c r="V5" t="s">
-        <v>93</v>
       </c>
       <c r="W5" t="s">
         <v>36</v>
@@ -1325,19 +1301,19 @@
         <v>35</v>
       </c>
       <c r="Y5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="Z5" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AA5" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AB5" t="s">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="AC5" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="AD5" t="s">
         <v>30</v>
@@ -1345,91 +1321,91 @@
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F6" t="s">
+        <v>97</v>
+      </c>
+      <c r="G6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I6" t="s">
+        <v>97</v>
+      </c>
+      <c r="J6" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" t="s">
+        <v>98</v>
+      </c>
+      <c r="L6" t="s">
         <v>99</v>
-      </c>
-      <c r="B6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F6" t="s">
-        <v>103</v>
-      </c>
-      <c r="G6" t="s">
-        <v>103</v>
-      </c>
-      <c r="H6" t="s">
-        <v>103</v>
-      </c>
-      <c r="I6" t="s">
-        <v>103</v>
-      </c>
-      <c r="J6" t="s">
-        <v>35</v>
-      </c>
-      <c r="K6" t="s">
-        <v>35</v>
-      </c>
-      <c r="L6" t="s">
-        <v>104</v>
       </c>
       <c r="M6" t="s">
         <v>37</v>
       </c>
       <c r="N6" t="s">
+        <v>99</v>
+      </c>
+      <c r="O6" t="s">
+        <v>100</v>
+      </c>
+      <c r="P6" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>101</v>
+      </c>
+      <c r="R6" t="s">
+        <v>102</v>
+      </c>
+      <c r="S6" t="s">
+        <v>35</v>
+      </c>
+      <c r="T6" t="s">
+        <v>41</v>
+      </c>
+      <c r="U6" t="s">
+        <v>103</v>
+      </c>
+      <c r="V6" t="s">
+        <v>83</v>
+      </c>
+      <c r="W6" t="s">
+        <v>35</v>
+      </c>
+      <c r="X6" t="s">
         <v>104</v>
       </c>
-      <c r="O6" t="s">
+      <c r="Y6" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA6" t="s">
         <v>105</v>
       </c>
-      <c r="P6" t="s">
+      <c r="AB6" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC6" t="s">
         <v>106</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>107</v>
-      </c>
-      <c r="R6" t="s">
-        <v>108</v>
-      </c>
-      <c r="S6" t="s">
-        <v>35</v>
-      </c>
-      <c r="T6" t="s">
-        <v>42</v>
-      </c>
-      <c r="U6" t="s">
-        <v>109</v>
-      </c>
-      <c r="V6" t="s">
-        <v>87</v>
-      </c>
-      <c r="W6" t="s">
-        <v>35</v>
-      </c>
-      <c r="X6" t="s">
-        <v>110</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>111</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>106</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>112</v>
       </c>
       <c r="AD6" t="s">
         <v>30</v>
@@ -1437,37 +1413,37 @@
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B7" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D7" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E7" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F7" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G7" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="H7" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="I7" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="J7" t="s">
         <v>35</v>
       </c>
       <c r="K7" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L7" t="s">
         <v>36</v>
@@ -1479,25 +1455,25 @@
         <v>37</v>
       </c>
       <c r="O7" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="P7" t="s">
-        <v>119</v>
+        <v>30</v>
       </c>
       <c r="Q7" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="R7" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="S7" t="s">
         <v>35</v>
       </c>
       <c r="T7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U7" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="V7" t="s">
         <v>35</v>
@@ -1515,13 +1491,13 @@
         <v>35</v>
       </c>
       <c r="AA7" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="AB7" t="s">
-        <v>119</v>
+        <v>30</v>
       </c>
       <c r="AC7" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="AD7" t="s">
         <v>30</v>
@@ -1529,37 +1505,37 @@
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B8" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C8" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D8" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E8" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F8" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="G8" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="H8" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="I8" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="J8" t="s">
         <v>35</v>
       </c>
       <c r="K8" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L8" t="s">
         <v>36</v>
@@ -1571,49 +1547,49 @@
         <v>37</v>
       </c>
       <c r="O8" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="P8" t="s">
-        <v>131</v>
+        <v>30</v>
       </c>
       <c r="Q8" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="R8" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="S8" t="s">
         <v>35</v>
       </c>
       <c r="T8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U8" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="V8" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="W8" t="s">
         <v>35</v>
       </c>
       <c r="X8" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="Y8" t="s">
         <v>35</v>
       </c>
       <c r="Z8" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="AA8" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="AB8" t="s">
-        <v>131</v>
+        <v>30</v>
       </c>
       <c r="AC8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="AD8" t="s">
         <v>30</v>
@@ -1644,7 +1620,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -1662,10 +1638,10 @@
         <v>15</v>
       </c>
       <c r="G1" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="H1" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="I1" t="s">
         <v>2</v>
@@ -1679,7 +1655,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B2" t="s">
         <v>31</v>
@@ -1694,19 +1670,19 @@
         <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="G2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="H2" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="I2" t="s">
         <v>32</v>
       </c>
       <c r="J2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K2" t="s">
         <v>30</v>
@@ -1714,34 +1690,34 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" t="s">
+        <v>136</v>
+      </c>
+      <c r="H3" t="s">
+        <v>137</v>
+      </c>
+      <c r="I3" t="s">
         <v>49</v>
       </c>
-      <c r="C3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G3" t="s">
-        <v>144</v>
-      </c>
-      <c r="H3" t="s">
-        <v>145</v>
-      </c>
-      <c r="I3" t="s">
-        <v>50</v>
-      </c>
       <c r="J3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K3" t="s">
         <v>30</v>
@@ -1749,34 +1725,34 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" t="s">
         <v>64</v>
       </c>
-      <c r="C4" t="s">
-        <v>66</v>
-      </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F4" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="G4" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="H4" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="I4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K4" t="s">
         <v>30</v>
@@ -1784,34 +1760,34 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>140</v>
+      </c>
+      <c r="H5" t="s">
         <v>141</v>
       </c>
-      <c r="B5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" t="s">
-        <v>88</v>
-      </c>
-      <c r="F5" t="s">
-        <v>89</v>
-      </c>
-      <c r="G5" t="s">
-        <v>148</v>
-      </c>
-      <c r="H5" t="s">
-        <v>149</v>
-      </c>
       <c r="I5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="J5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K5" t="s">
         <v>30</v>
@@ -1819,34 +1795,34 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" t="s">
         <v>100</v>
       </c>
-      <c r="C6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D6" t="s">
-        <v>103</v>
-      </c>
-      <c r="E6" t="s">
-        <v>105</v>
-      </c>
       <c r="F6" t="s">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="G6" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="H6" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="I6" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="J6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K6" t="s">
         <v>30</v>
@@ -1854,34 +1830,34 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B7" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D7" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E7" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="F7" t="s">
-        <v>119</v>
+        <v>30</v>
       </c>
       <c r="G7" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H7" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="I7" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="J7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K7" t="s">
         <v>30</v>
@@ -1889,34 +1865,34 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B8" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C8" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D8" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E8" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="F8" t="s">
-        <v>131</v>
+        <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="H8" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="I8" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="J8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K8" t="s">
         <v>30</v>
@@ -1947,7 +1923,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -1965,10 +1941,10 @@
         <v>15</v>
       </c>
       <c r="G1" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="H1" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="I1" t="s">
         <v>2</v>
@@ -1982,7 +1958,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B2" t="s">
         <v>31</v>
@@ -1997,19 +1973,19 @@
         <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="G2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="H2" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="I2" t="s">
         <v>32</v>
       </c>
       <c r="J2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K2" t="s">
         <v>30</v>
@@ -2017,34 +1993,34 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" t="s">
+        <v>136</v>
+      </c>
+      <c r="H3" t="s">
+        <v>137</v>
+      </c>
+      <c r="I3" t="s">
         <v>49</v>
       </c>
-      <c r="C3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G3" t="s">
-        <v>144</v>
-      </c>
-      <c r="H3" t="s">
-        <v>145</v>
-      </c>
-      <c r="I3" t="s">
-        <v>50</v>
-      </c>
       <c r="J3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K3" t="s">
         <v>30</v>
@@ -2052,34 +2028,34 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" t="s">
         <v>64</v>
       </c>
-      <c r="C4" t="s">
-        <v>66</v>
-      </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F4" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="G4" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="H4" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="I4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K4" t="s">
         <v>30</v>
@@ -2087,34 +2063,34 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>140</v>
+      </c>
+      <c r="H5" t="s">
         <v>141</v>
       </c>
-      <c r="B5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" t="s">
-        <v>88</v>
-      </c>
-      <c r="F5" t="s">
-        <v>89</v>
-      </c>
-      <c r="G5" t="s">
-        <v>148</v>
-      </c>
-      <c r="H5" t="s">
-        <v>149</v>
-      </c>
       <c r="I5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="J5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K5" t="s">
         <v>30</v>
@@ -2122,34 +2098,34 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" t="s">
         <v>100</v>
       </c>
-      <c r="C6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D6" t="s">
-        <v>103</v>
-      </c>
-      <c r="E6" t="s">
-        <v>105</v>
-      </c>
       <c r="F6" t="s">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="G6" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="H6" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="I6" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="J6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K6" t="s">
         <v>30</v>
@@ -2157,34 +2133,34 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B7" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D7" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E7" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="F7" t="s">
-        <v>119</v>
+        <v>30</v>
       </c>
       <c r="G7" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H7" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="I7" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="J7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K7" t="s">
         <v>30</v>
@@ -2192,34 +2168,34 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B8" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C8" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D8" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E8" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="F8" t="s">
-        <v>131</v>
+        <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="H8" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="I8" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="J8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K8" t="s">
         <v>30</v>

--- a/data/broker/broker_quote_2026-07-22.xlsx
+++ b/data/broker/broker_quote_2026-07-22.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="158">
   <si>
     <t>类型</t>
   </si>
@@ -294,9 +294,6 @@
     <t>2026-04-20</t>
   </si>
   <si>
-    <t>S</t>
-  </si>
-  <si>
     <t>26长春轨交MTN006</t>
   </si>
   <si>
@@ -309,34 +306,70 @@
     <t>3.0200</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>2.9578</t>
+  </si>
+  <si>
+    <t>09:03:51</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>100.8120</t>
+  </si>
+  <si>
+    <t>0.6005</t>
+  </si>
+  <si>
+    <t>招商银行股份有限公司</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>24泰丰02</t>
+  </si>
+  <si>
+    <t>254402.SH</t>
+  </si>
+  <si>
+    <t>2.79Y</t>
+  </si>
+  <si>
+    <t>3.0000</t>
+  </si>
+  <si>
     <t>2.00</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>2.9578</t>
-  </si>
-  <si>
-    <t>09:03:51</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>100.8120</t>
-  </si>
-  <si>
-    <t>0.6005</t>
-  </si>
-  <si>
-    <t>招商银行股份有限公司</t>
-  </si>
-  <si>
-    <t>2026-05-26</t>
-  </si>
-  <si>
-    <t>全部利率</t>
+    <t>2.9796</t>
+  </si>
+  <si>
+    <t>08:24:46</t>
+  </si>
+  <si>
+    <t>新泰市财金投资集团有限公司</t>
+  </si>
+  <si>
+    <t>107.6422</t>
+  </si>
+  <si>
+    <t>23.24</t>
+  </si>
+  <si>
+    <t>13939.45</t>
+  </si>
+  <si>
+    <t>8/14</t>
+  </si>
+  <si>
+    <t>申港证券股份有限公司</t>
+  </si>
+  <si>
+    <t>2024-05-07</t>
   </si>
   <si>
     <t>25陕建集团SCP012(科创债)</t>
@@ -348,9 +381,6 @@
     <t>9D</t>
   </si>
   <si>
-    <t>3.0000</t>
-  </si>
-  <si>
     <t>2.9890</t>
   </si>
   <si>
@@ -369,9 +399,6 @@
     <t>2025-11-02</t>
   </si>
   <si>
-    <t>地方债</t>
-  </si>
-  <si>
     <t>26鲁商MTN001</t>
   </si>
   <si>
@@ -447,6 +474,12 @@
     <t>吉林</t>
   </si>
   <si>
+    <t>山东泰丰控股集团有限公司</t>
+  </si>
+  <si>
+    <t>山东</t>
+  </si>
+  <si>
     <t>陕西建工集团股份有限公司</t>
   </si>
   <si>
@@ -454,9 +487,6 @@
   </si>
   <si>
     <t>山东省商业集团有限公司</t>
-  </si>
-  <si>
-    <t>山东</t>
   </si>
 </sst>
 </file>
@@ -833,7 +863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD8"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1321,58 +1351,58 @@
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
         <v>93</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>94</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>95</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>96</v>
       </c>
-      <c r="E6" t="s">
-        <v>97</v>
-      </c>
       <c r="F6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J6" t="s">
         <v>35</v>
       </c>
       <c r="K6" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="L6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="M6" t="s">
         <v>37</v>
       </c>
       <c r="N6" t="s">
+        <v>97</v>
+      </c>
+      <c r="O6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P6" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q6" t="s">
         <v>99</v>
       </c>
-      <c r="O6" t="s">
+      <c r="R6" t="s">
         <v>100</v>
-      </c>
-      <c r="P6" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>101</v>
-      </c>
-      <c r="R6" t="s">
-        <v>102</v>
       </c>
       <c r="S6" t="s">
         <v>35</v>
@@ -1381,7 +1411,7 @@
         <v>41</v>
       </c>
       <c r="U6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="V6" t="s">
         <v>83</v>
@@ -1390,7 +1420,7 @@
         <v>35</v>
       </c>
       <c r="X6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="Y6" t="s">
         <v>35</v>
@@ -1399,13 +1429,13 @@
         <v>45</v>
       </c>
       <c r="AA6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="AB6" t="s">
         <v>30</v>
       </c>
       <c r="AC6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AD6" t="s">
         <v>30</v>
@@ -1413,37 +1443,37 @@
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" t="s">
         <v>107</v>
       </c>
-      <c r="B7" t="s">
+      <c r="E7" t="s">
+        <v>96</v>
+      </c>
+      <c r="F7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G7" t="s">
+        <v>96</v>
+      </c>
+      <c r="H7" t="s">
+        <v>96</v>
+      </c>
+      <c r="I7" t="s">
+        <v>96</v>
+      </c>
+      <c r="J7" t="s">
         <v>108</v>
       </c>
-      <c r="C7" t="s">
+      <c r="K7" t="s">
         <v>109</v>
-      </c>
-      <c r="D7" t="s">
-        <v>110</v>
-      </c>
-      <c r="E7" t="s">
-        <v>111</v>
-      </c>
-      <c r="F7" t="s">
-        <v>111</v>
-      </c>
-      <c r="G7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H7" t="s">
-        <v>111</v>
-      </c>
-      <c r="I7" t="s">
-        <v>111</v>
-      </c>
-      <c r="J7" t="s">
-        <v>35</v>
-      </c>
-      <c r="K7" t="s">
-        <v>30</v>
       </c>
       <c r="L7" t="s">
         <v>36</v>
@@ -1455,49 +1485,49 @@
         <v>37</v>
       </c>
       <c r="O7" t="s">
+        <v>110</v>
+      </c>
+      <c r="P7" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>111</v>
+      </c>
+      <c r="R7" t="s">
+        <v>70</v>
+      </c>
+      <c r="S7" t="s">
         <v>112</v>
-      </c>
-      <c r="P7" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>113</v>
-      </c>
-      <c r="R7" t="s">
-        <v>114</v>
-      </c>
-      <c r="S7" t="s">
-        <v>35</v>
       </c>
       <c r="T7" t="s">
         <v>41</v>
       </c>
       <c r="U7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="V7" t="s">
-        <v>35</v>
+        <v>114</v>
       </c>
       <c r="W7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X7" t="s">
         <v>35</v>
       </c>
       <c r="Y7" t="s">
-        <v>35</v>
+        <v>115</v>
       </c>
       <c r="Z7" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="AA7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AB7" t="s">
         <v>30</v>
       </c>
       <c r="AC7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AD7" t="s">
         <v>30</v>
@@ -1505,7 +1535,7 @@
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>118</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
         <v>119</v>
@@ -1517,19 +1547,19 @@
         <v>121</v>
       </c>
       <c r="E8" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="F8" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="G8" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="H8" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="I8" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="J8" t="s">
         <v>35</v>
@@ -1547,16 +1577,16 @@
         <v>37</v>
       </c>
       <c r="O8" t="s">
+        <v>122</v>
+      </c>
+      <c r="P8" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q8" t="s">
         <v>123</v>
       </c>
-      <c r="P8" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q8" t="s">
+      <c r="R8" t="s">
         <v>124</v>
-      </c>
-      <c r="R8" t="s">
-        <v>102</v>
       </c>
       <c r="S8" t="s">
         <v>35</v>
@@ -1568,30 +1598,122 @@
         <v>125</v>
       </c>
       <c r="V8" t="s">
-        <v>126</v>
+        <v>35</v>
       </c>
       <c r="W8" t="s">
         <v>35</v>
       </c>
       <c r="X8" t="s">
-        <v>127</v>
+        <v>35</v>
       </c>
       <c r="Y8" t="s">
         <v>35</v>
       </c>
       <c r="Z8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>127</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
         <v>128</v>
       </c>
-      <c r="AA8" t="s">
+      <c r="C9" t="s">
         <v>129</v>
       </c>
-      <c r="AB8" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC8" t="s">
+      <c r="D9" t="s">
+        <v>130</v>
+      </c>
+      <c r="E9" t="s">
+        <v>131</v>
+      </c>
+      <c r="F9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G9" t="s">
+        <v>131</v>
+      </c>
+      <c r="H9" t="s">
+        <v>131</v>
+      </c>
+      <c r="I9" t="s">
+        <v>131</v>
+      </c>
+      <c r="J9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" t="s">
+        <v>30</v>
+      </c>
+      <c r="L9" t="s">
+        <v>36</v>
+      </c>
+      <c r="M9" t="s">
+        <v>36</v>
+      </c>
+      <c r="N9" t="s">
+        <v>37</v>
+      </c>
+      <c r="O9" t="s">
+        <v>132</v>
+      </c>
+      <c r="P9" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>133</v>
+      </c>
+      <c r="R9" t="s">
+        <v>100</v>
+      </c>
+      <c r="S9" t="s">
+        <v>35</v>
+      </c>
+      <c r="T9" t="s">
+        <v>41</v>
+      </c>
+      <c r="U9" t="s">
+        <v>134</v>
+      </c>
+      <c r="V9" t="s">
+        <v>135</v>
+      </c>
+      <c r="W9" t="s">
+        <v>35</v>
+      </c>
+      <c r="X9" t="s">
+        <v>136</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>138</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC9" t="s">
         <v>92</v>
       </c>
-      <c r="AD8" t="s">
+      <c r="AD9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1603,7 +1725,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1620,7 +1742,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -1638,10 +1760,10 @@
         <v>15</v>
       </c>
       <c r="G1" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H1" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="I1" t="s">
         <v>2</v>
@@ -1655,7 +1777,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B2" t="s">
         <v>31</v>
@@ -1673,10 +1795,10 @@
         <v>30</v>
       </c>
       <c r="G2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="H2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="I2" t="s">
         <v>32</v>
@@ -1690,7 +1812,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B3" t="s">
         <v>48</v>
@@ -1708,10 +1830,10 @@
         <v>30</v>
       </c>
       <c r="G3" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="H3" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="I3" t="s">
         <v>49</v>
@@ -1725,7 +1847,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
@@ -1743,10 +1865,10 @@
         <v>30</v>
       </c>
       <c r="G4" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="H4" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="I4" t="s">
         <v>63</v>
@@ -1760,7 +1882,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B5" t="s">
         <v>78</v>
@@ -1778,10 +1900,10 @@
         <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="H5" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I5" t="s">
         <v>79</v>
@@ -1795,31 +1917,31 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
+        <v>151</v>
+      </c>
+      <c r="H6" t="s">
+        <v>152</v>
+      </c>
+      <c r="I6" t="s">
         <v>94</v>
-      </c>
-      <c r="C6" t="s">
-        <v>96</v>
-      </c>
-      <c r="D6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E6" t="s">
-        <v>100</v>
-      </c>
-      <c r="F6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" t="s">
-        <v>142</v>
-      </c>
-      <c r="H6" t="s">
-        <v>143</v>
-      </c>
-      <c r="I6" t="s">
-        <v>95</v>
       </c>
       <c r="J6" t="s">
         <v>41</v>
@@ -1830,31 +1952,31 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B7" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" t="s">
         <v>110</v>
       </c>
-      <c r="D7" t="s">
-        <v>111</v>
-      </c>
-      <c r="E7" t="s">
-        <v>112</v>
-      </c>
       <c r="F7" t="s">
         <v>30</v>
       </c>
       <c r="G7" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="H7" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="I7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J7" t="s">
         <v>41</v>
@@ -1865,7 +1987,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B8" t="s">
         <v>119</v>
@@ -1874,19 +1996,19 @@
         <v>121</v>
       </c>
       <c r="D8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E8" t="s">
         <v>122</v>
       </c>
-      <c r="E8" t="s">
-        <v>123</v>
-      </c>
       <c r="F8" t="s">
         <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="H8" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="I8" t="s">
         <v>120</v>
@@ -1895,6 +2017,41 @@
         <v>41</v>
       </c>
       <c r="K8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>142</v>
+      </c>
+      <c r="B9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C9" t="s">
+        <v>130</v>
+      </c>
+      <c r="D9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E9" t="s">
+        <v>132</v>
+      </c>
+      <c r="F9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" t="s">
+        <v>157</v>
+      </c>
+      <c r="H9" t="s">
+        <v>154</v>
+      </c>
+      <c r="I9" t="s">
+        <v>129</v>
+      </c>
+      <c r="J9" t="s">
+        <v>41</v>
+      </c>
+      <c r="K9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1906,7 +2063,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1923,7 +2080,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -1941,10 +2098,10 @@
         <v>15</v>
       </c>
       <c r="G1" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H1" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="I1" t="s">
         <v>2</v>
@@ -1958,7 +2115,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B2" t="s">
         <v>31</v>
@@ -1976,10 +2133,10 @@
         <v>30</v>
       </c>
       <c r="G2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="H2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="I2" t="s">
         <v>32</v>
@@ -1993,7 +2150,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B3" t="s">
         <v>48</v>
@@ -2011,10 +2168,10 @@
         <v>30</v>
       </c>
       <c r="G3" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="H3" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="I3" t="s">
         <v>49</v>
@@ -2028,7 +2185,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
@@ -2046,10 +2203,10 @@
         <v>30</v>
       </c>
       <c r="G4" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="H4" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="I4" t="s">
         <v>63</v>
@@ -2063,7 +2220,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B5" t="s">
         <v>78</v>
@@ -2081,10 +2238,10 @@
         <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="H5" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="I5" t="s">
         <v>79</v>
@@ -2098,31 +2255,31 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
+        <v>151</v>
+      </c>
+      <c r="H6" t="s">
+        <v>152</v>
+      </c>
+      <c r="I6" t="s">
         <v>94</v>
-      </c>
-      <c r="C6" t="s">
-        <v>96</v>
-      </c>
-      <c r="D6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E6" t="s">
-        <v>100</v>
-      </c>
-      <c r="F6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" t="s">
-        <v>142</v>
-      </c>
-      <c r="H6" t="s">
-        <v>143</v>
-      </c>
-      <c r="I6" t="s">
-        <v>95</v>
       </c>
       <c r="J6" t="s">
         <v>41</v>
@@ -2133,31 +2290,31 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B7" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" t="s">
         <v>110</v>
       </c>
-      <c r="D7" t="s">
-        <v>111</v>
-      </c>
-      <c r="E7" t="s">
-        <v>112</v>
-      </c>
       <c r="F7" t="s">
         <v>30</v>
       </c>
       <c r="G7" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="H7" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="I7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J7" t="s">
         <v>41</v>
@@ -2168,7 +2325,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B8" t="s">
         <v>119</v>
@@ -2177,19 +2334,19 @@
         <v>121</v>
       </c>
       <c r="D8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E8" t="s">
         <v>122</v>
       </c>
-      <c r="E8" t="s">
-        <v>123</v>
-      </c>
       <c r="F8" t="s">
         <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="H8" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="I8" t="s">
         <v>120</v>
@@ -2198,6 +2355,41 @@
         <v>41</v>
       </c>
       <c r="K8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>142</v>
+      </c>
+      <c r="B9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C9" t="s">
+        <v>130</v>
+      </c>
+      <c r="D9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E9" t="s">
+        <v>132</v>
+      </c>
+      <c r="F9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" t="s">
+        <v>157</v>
+      </c>
+      <c r="H9" t="s">
+        <v>154</v>
+      </c>
+      <c r="I9" t="s">
+        <v>129</v>
+      </c>
+      <c r="J9" t="s">
+        <v>41</v>
+      </c>
+      <c r="K9" t="s">
         <v>30</v>
       </c>
     </row>

--- a/data/broker/broker_quote_2026-07-22.xlsx
+++ b/data/broker/broker_quote_2026-07-22.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="166">
   <si>
     <t>类型</t>
   </si>
@@ -444,46 +444,70 @@
     <t>2026-7-22</t>
   </si>
   <si>
+    <t>1.29</t>
+  </si>
+  <si>
     <t>云南省能源集团有限公司</t>
   </si>
   <si>
     <t>云南</t>
   </si>
   <si>
+    <t>4.23</t>
+  </si>
+  <si>
     <t>太原重型机械集团有限公司</t>
   </si>
   <si>
     <t>山西</t>
   </si>
   <si>
+    <t>3.26</t>
+  </si>
+  <si>
     <t>兰州新区城市发展投资集团有限公司</t>
   </si>
   <si>
     <t>甘肃</t>
   </si>
   <si>
+    <t>7.03</t>
+  </si>
+  <si>
     <t>贵阳经济开发区城市建设投资(集团)股份有限公司</t>
   </si>
   <si>
     <t>贵州</t>
   </si>
   <si>
+    <t>6.22</t>
+  </si>
+  <si>
     <t>长春市轨道交通集团有限公司</t>
   </si>
   <si>
     <t>吉林</t>
   </si>
   <si>
+    <t>4.04</t>
+  </si>
+  <si>
     <t>山东泰丰控股集团有限公司</t>
   </si>
   <si>
     <t>山东</t>
   </si>
   <si>
+    <t>1.10</t>
+  </si>
+  <si>
     <t>陕西建工集团股份有限公司</t>
   </si>
   <si>
     <t>陕西</t>
+  </si>
+  <si>
+    <t>8.25</t>
   </si>
   <si>
     <t>山东省商业集团有限公司</t>
@@ -1792,13 +1816,13 @@
         <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>143</v>
       </c>
       <c r="G2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I2" t="s">
         <v>32</v>
@@ -1827,13 +1851,13 @@
         <v>53</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>146</v>
       </c>
       <c r="G3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I3" t="s">
         <v>49</v>
@@ -1862,13 +1886,13 @@
         <v>68</v>
       </c>
       <c r="F4" t="s">
-        <v>30</v>
+        <v>149</v>
       </c>
       <c r="G4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="I4" t="s">
         <v>63</v>
@@ -1897,13 +1921,13 @@
         <v>84</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>152</v>
       </c>
       <c r="G5" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H5" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="I5" t="s">
         <v>79</v>
@@ -1932,13 +1956,13 @@
         <v>98</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>155</v>
       </c>
       <c r="G6" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="H6" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I6" t="s">
         <v>94</v>
@@ -1967,13 +1991,13 @@
         <v>110</v>
       </c>
       <c r="F7" t="s">
-        <v>30</v>
+        <v>158</v>
       </c>
       <c r="G7" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="H7" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="I7" t="s">
         <v>106</v>
@@ -2002,13 +2026,13 @@
         <v>122</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>161</v>
       </c>
       <c r="G8" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="H8" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="I8" t="s">
         <v>120</v>
@@ -2037,13 +2061,13 @@
         <v>132</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>164</v>
       </c>
       <c r="G9" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H9" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="I9" t="s">
         <v>129</v>
@@ -2130,13 +2154,13 @@
         <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>143</v>
       </c>
       <c r="G2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I2" t="s">
         <v>32</v>
@@ -2165,13 +2189,13 @@
         <v>53</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>146</v>
       </c>
       <c r="G3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I3" t="s">
         <v>49</v>
@@ -2200,13 +2224,13 @@
         <v>68</v>
       </c>
       <c r="F4" t="s">
-        <v>30</v>
+        <v>149</v>
       </c>
       <c r="G4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="I4" t="s">
         <v>63</v>
@@ -2235,13 +2259,13 @@
         <v>84</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>152</v>
       </c>
       <c r="G5" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H5" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="I5" t="s">
         <v>79</v>
@@ -2270,13 +2294,13 @@
         <v>98</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>155</v>
       </c>
       <c r="G6" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="H6" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I6" t="s">
         <v>94</v>
@@ -2305,13 +2329,13 @@
         <v>110</v>
       </c>
       <c r="F7" t="s">
-        <v>30</v>
+        <v>158</v>
       </c>
       <c r="G7" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="H7" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="I7" t="s">
         <v>106</v>
@@ -2340,13 +2364,13 @@
         <v>122</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>161</v>
       </c>
       <c r="G8" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="H8" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="I8" t="s">
         <v>120</v>
@@ -2375,13 +2399,13 @@
         <v>132</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>164</v>
       </c>
       <c r="G9" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H9" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="I9" t="s">
         <v>129</v>
